--- a/sql-scripts/Dataset_Sprint_1_ com inserts.xlsx
+++ b/sql-scripts/Dataset_Sprint_1_ com inserts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myisepipp-my.sharepoint.com/personal/1221267_isep_ipp_pt/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael\IdeaProjects\sem-pi-25-26-g054\sql-scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="478" documentId="8_{1D45F37E-73D0-49D5-81ED-3AA71E0EC2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80AD8D2F-5393-4334-B573-6FB63E81E363}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CCE598-4132-4730-B8CA-5A79B652FF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="5" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="1" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility" sheetId="1" r:id="rId1"/>
@@ -487,14 +487,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -927,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="str">
-        <f t="shared" ref="D8:D29" si="0">"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A4&amp;", '"&amp;B4&amp;"',1);"</f>
+        <f t="shared" ref="D9:D29" si="0">"INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES ("&amp;A4&amp;", '"&amp;B4&amp;"',1);"</f>
         <v>INSERT INTO Station (idStation, nameStation, stationTypeId) VALUES (3, 'Senhora das Dores',1);</v>
       </c>
     </row>
@@ -1213,8 +1212,8 @@
         <v>1668</v>
       </c>
       <c r="K2" t="str">
-        <f>"INSERT INTO Gauge (idGauge, name, measure) VALUES (1,'Iberian gauge', '"&amp;H3&amp;"');"</f>
-        <v>INSERT INTO Gauge (idGauge, name, measure) VALUES (1,'Iberian gauge', '1668');</v>
+        <f>"INSERT INTO Gauge (idGauge, measure) VALUES (1,'"&amp;H3&amp;"');"</f>
+        <v>INSERT INTO Gauge (idGauge, measure) VALUES (1,'1668');</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.4">
@@ -1243,8 +1242,8 @@
         <v>1668</v>
       </c>
       <c r="K3" t="str">
-        <f>"INSERT INTO Gauge (idGauge, name, measure) VALUES (2,'Standard Gauge', '"&amp;'Wagon Model'!N8&amp;"');"</f>
-        <v>INSERT INTO Gauge (idGauge, name, measure) VALUES (2,'Standard Gauge', '1435');</v>
+        <f>"INSERT INTO Gauge (idGauge, measure) VALUES (2,'"&amp;'Wagon Model'!N8&amp;"');"</f>
+        <v>INSERT INTO Gauge (idGauge, measure) VALUES (2,'1435');</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.4">
@@ -1417,6 +1416,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1768,78 +1768,79 @@
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B18" t="str">
-        <f t="shared" ref="B18:B29" si="0">"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A3&amp;","&amp;E3&amp;","&amp;F3&amp;",1,"&amp;C3&amp;",2,"&amp;B3&amp;");"</f>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (10,8000,29003,1,1,2,2);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A3&amp;","&amp;E3&amp;","&amp;F3&amp;",1,"&amp;C3&amp;",1,"&amp;B3&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (10,8000,29003,1,1,1,2);</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B19" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (11,8000,10000,1,2,2,2);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A4&amp;","&amp;E4&amp;","&amp;F4&amp;",1,"&amp;C4&amp;",1,"&amp;B4&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (11,8000,10000,1,2,1,2);</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B20" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (15,8000,5286,1,1,2,3);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A5&amp;","&amp;E5&amp;","&amp;F5&amp;",1,"&amp;C5&amp;",1,"&amp;B5&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (15,8000,5286,1,1,1,3);</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (16,8000,6000,1,2,2,3);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A6&amp;","&amp;E6&amp;","&amp;F6&amp;",1,"&amp;C6&amp;",1,"&amp;B6&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (16,8000,6000,1,2,1,3);</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B22" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (14,8000,10387,1,1,2,4);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A7&amp;","&amp;E7&amp;","&amp;F7&amp;",1,"&amp;C7&amp;",1,"&amp;B7&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (14,8000,10387,1,1,1,4);</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B23" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (12,8000,12000,1,2,2,4);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A8&amp;","&amp;E8&amp;","&amp;F8&amp;",1,"&amp;C8&amp;",1,"&amp;B8&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (12,8000,12000,1,2,1,4);</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B24" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (13,6400,8000,1,3,2,4);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A9&amp;","&amp;E9&amp;","&amp;F9&amp;",1,"&amp;C9&amp;",1,"&amp;B9&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (13,6400,8000,1,3,1,4);</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B25" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (20,8000,6000,1,1,2,5);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A10&amp;","&amp;E10&amp;","&amp;F10&amp;",1,"&amp;C10&amp;",1,"&amp;B10&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (20,8000,6000,1,1,1,5);</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B26" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (21,8000,3000,1,2,2,5);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A11&amp;","&amp;E11&amp;","&amp;F11&amp;",1,"&amp;C11&amp;",1,"&amp;B11&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (21,8000,3000,1,2,1,5);</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B27" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (22,8000,15000,1,3,2,5);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A12&amp;","&amp;E12&amp;","&amp;F12&amp;",1,"&amp;C12&amp;",1,"&amp;B12&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (22,8000,15000,1,3,1,5);</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B28" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (25,8000,20829,1,1,2,6);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A13&amp;","&amp;E13&amp;","&amp;F13&amp;",1,"&amp;C13&amp;",1,"&amp;B13&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (25,8000,20829,1,1,1,6);</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B29" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (26,8000,4264,1,1,2,7);</v>
+        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A14&amp;","&amp;E14&amp;","&amp;F14&amp;",1,"&amp;C14&amp;",1,"&amp;B14&amp;");"</f>
+        <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (26,8000,4264,1,1,1,7);</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2811,7 +2812,7 @@
         <v>1987</v>
       </c>
       <c r="G2" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A2&amp;", 21.2,"&amp;D2&amp;",1104,'PT509017800');"</f>
+        <f t="shared" ref="G2:G17" si="0">"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A2&amp;", 21.2,"&amp;D2&amp;",1104,'PT509017800');"</f>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563077, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -2829,7 +2830,7 @@
         <v>1987</v>
       </c>
       <c r="G3" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A3&amp;", 21.2,"&amp;D3&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563078, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -2847,7 +2848,7 @@
         <v>1987</v>
       </c>
       <c r="G4" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A4&amp;", 21.2,"&amp;D4&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563079, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -2865,7 +2866,7 @@
         <v>1987</v>
       </c>
       <c r="G5" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A5&amp;", 21.2,"&amp;D5&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563080, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -2883,7 +2884,7 @@
         <v>1987</v>
       </c>
       <c r="G6" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A6&amp;", 21.2,"&amp;D6&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563081, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -2901,7 +2902,7 @@
         <v>1987</v>
       </c>
       <c r="G7" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A7&amp;", 21.2,"&amp;D7&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563082, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -2919,7 +2920,7 @@
         <v>1987</v>
       </c>
       <c r="G8" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A8&amp;", 21.2,"&amp;D8&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563083, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -2937,7 +2938,7 @@
         <v>1987</v>
       </c>
       <c r="G9" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A9&amp;", 21.2,"&amp;D9&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563084, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -2955,7 +2956,7 @@
         <v>1987</v>
       </c>
       <c r="G10" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A10&amp;", 21.2,"&amp;D10&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563085, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -2974,12 +2975,12 @@
       </c>
       <c r="F11" s="4"/>
       <c r="G11" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A11&amp;", 21.2,"&amp;D11&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563086, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A12" s="6">
+      <c r="A12">
         <v>3563087</v>
       </c>
       <c r="B12" t="s">
@@ -2992,7 +2993,7 @@
         <v>1987</v>
       </c>
       <c r="G12" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A12&amp;", 21.2,"&amp;D12&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563087, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -3010,7 +3011,7 @@
         <v>1987</v>
       </c>
       <c r="G13" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A13&amp;", 21.2,"&amp;D13&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563088, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -3028,7 +3029,7 @@
         <v>1987</v>
       </c>
       <c r="G14" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A14&amp;", 21.2,"&amp;D14&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563089, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -3046,7 +3047,7 @@
         <v>1987</v>
       </c>
       <c r="G15" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A15&amp;", 21.2,"&amp;D15&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563090, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -3064,7 +3065,7 @@
         <v>1987</v>
       </c>
       <c r="G16" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A16&amp;", 21.2,"&amp;D16&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563091, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -3082,7 +3083,7 @@
         <v>1987</v>
       </c>
       <c r="G17" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A17&amp;", 21.2,"&amp;D17&amp;",1104,'PT509017800');"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (3563092, 21.2,1987,1104,'PT509017800');</v>
       </c>
     </row>
@@ -3172,7 +3173,7 @@
         <v>1977</v>
       </c>
       <c r="G22" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A22&amp;",13.8,"&amp;D22&amp;",1278,'PT509017800');"</f>
+        <f t="shared" ref="G22:G27" si="1">"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A22&amp;",13.8,"&amp;D22&amp;",1278,'PT509017800');"</f>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (741001,13.8,1977,1278,'PT509017800');</v>
       </c>
     </row>
@@ -3190,7 +3191,7 @@
         <v>1977</v>
       </c>
       <c r="G23" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A23&amp;",13.8,"&amp;D23&amp;",1278,'PT509017800');"</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (741002,13.8,1977,1278,'PT509017800');</v>
       </c>
     </row>
@@ -3208,7 +3209,7 @@
         <v>1977</v>
       </c>
       <c r="G24" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A24&amp;",13.8,"&amp;D24&amp;",1278,'PT509017800');"</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (741003,13.8,1977,1278,'PT509017800');</v>
       </c>
     </row>
@@ -3226,7 +3227,7 @@
         <v>1977</v>
       </c>
       <c r="G25" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A25&amp;",13.8,"&amp;D25&amp;",1278,'PT509017800');"</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (741004,13.8,1977,1278,'PT509017800');</v>
       </c>
     </row>
@@ -3244,7 +3245,7 @@
         <v>1977</v>
       </c>
       <c r="G26" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A26&amp;",13.8,"&amp;D26&amp;",1278,'PT509017800');"</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (741005,13.8,1977,1278,'PT509017800');</v>
       </c>
     </row>
@@ -3262,7 +3263,7 @@
         <v>1977</v>
       </c>
       <c r="G27" t="str">
-        <f>"INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES ("&amp;A27&amp;",13.8,"&amp;D27&amp;",1278,'PT509017800');"</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO Wagon (numberWagon, weight, yearOfEntry, wagonModelId, operator) VALUES (741006,13.8,1977,1278,'PT509017800');</v>
       </c>
     </row>

--- a/sql-scripts/Dataset_Sprint_1_ com inserts.xlsx
+++ b/sql-scripts/Dataset_Sprint_1_ com inserts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael\IdeaProjects\sem-pi-25-26-g054\sql-scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diogo\IdeaProjects\sem3-pi-25-26-g054-repo\sql-scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CCE598-4132-4730-B8CA-5A79B652FF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593F0165-5543-48D3-B6FF-C980A17B48A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="1" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility" sheetId="1" r:id="rId1"/>
@@ -1768,73 +1768,73 @@
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B18" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A3&amp;","&amp;E3&amp;","&amp;F3&amp;",1,"&amp;C3&amp;",1,"&amp;B3&amp;");"</f>
+        <f t="shared" ref="B18:B29" si="0">"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A3&amp;","&amp;E3&amp;","&amp;F3&amp;",1,"&amp;C3&amp;",1,"&amp;B3&amp;");"</f>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (10,8000,29003,1,1,1,2);</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B19" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A4&amp;","&amp;E4&amp;","&amp;F4&amp;",1,"&amp;C4&amp;",1,"&amp;B4&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (11,8000,10000,1,2,1,2);</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B20" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A5&amp;","&amp;E5&amp;","&amp;F5&amp;",1,"&amp;C5&amp;",1,"&amp;B5&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (15,8000,5286,1,1,1,3);</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A6&amp;","&amp;E6&amp;","&amp;F6&amp;",1,"&amp;C6&amp;",1,"&amp;B6&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (16,8000,6000,1,2,1,3);</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B22" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A7&amp;","&amp;E7&amp;","&amp;F7&amp;",1,"&amp;C7&amp;",1,"&amp;B7&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (14,8000,10387,1,1,1,4);</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B23" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A8&amp;","&amp;E8&amp;","&amp;F8&amp;",1,"&amp;C8&amp;",1,"&amp;B8&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (12,8000,12000,1,2,1,4);</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B24" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A9&amp;","&amp;E9&amp;","&amp;F9&amp;",1,"&amp;C9&amp;",1,"&amp;B9&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (13,6400,8000,1,3,1,4);</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B25" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A10&amp;","&amp;E10&amp;","&amp;F10&amp;",1,"&amp;C10&amp;",1,"&amp;B10&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (20,8000,6000,1,1,1,5);</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B26" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A11&amp;","&amp;E11&amp;","&amp;F11&amp;",1,"&amp;C11&amp;",1,"&amp;B11&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (21,8000,3000,1,2,1,5);</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B27" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A12&amp;","&amp;E12&amp;","&amp;F12&amp;",1,"&amp;C12&amp;",1,"&amp;B12&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (22,8000,15000,1,3,1,5);</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B28" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A13&amp;","&amp;E13&amp;","&amp;F13&amp;",1,"&amp;C13&amp;",1,"&amp;B13&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (25,8000,20829,1,1,1,6);</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B29" t="str">
-        <f>"INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES ("&amp;A14&amp;","&amp;E14&amp;","&amp;F14&amp;",1,"&amp;C14&amp;",1,"&amp;B14&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO LineSegment (id, maximumWeigh, lenght, isElectrified, segmantesOrder,lineSegmentsTypeid, lineId) VALUES (26,8000,4264,1,1,1,7);</v>
       </c>
     </row>

--- a/sql-scripts/Dataset_Sprint_1_ com inserts.xlsx
+++ b/sql-scripts/Dataset_Sprint_1_ com inserts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diogo\IdeaProjects\sem3-pi-25-26-g054-repo\sql-scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael\IdeaProjects\sem-pi-25-26-g054\sql-scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593F0165-5543-48D3-B6FF-C980A17B48A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A490D747-0529-4741-9567-08B759357A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="5" xr2:uid="{7F4AA980-AB96-5943-AE3E-BE2681F30F29}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility" sheetId="1" r:id="rId1"/>
@@ -487,13 +487,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2220,7 +2221,7 @@
       <c r="I5" t="s">
         <v>118</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="6" t="s">
         <v>119</v>
       </c>
       <c r="K5" t="s">
